--- a/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/vd-ingame-creator/vd_gom_normal_00001/vd_gom_normal_00001.xlsx
+++ b/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/vd-ingame-creator/vd_gom_normal_00001/vd_gom_normal_00001.xlsx
@@ -730,7 +730,7 @@
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="26" t="inlineStr">
         <is>
-          <t>「姫様“拷問”の時間です」の世界観を反映したノーマルブロックです。たこ焼き（Yellow属性・攻撃ロール）、バタートースト（Yellow属性・防御ロール）、ラーメン（Yellow属性・攻撃ロール）、ファントム（Colorless属性・攻撃ロール）の4種が時間差で出現します。同作の料理系の敵キャラを中心に構成することで作品らしいユーモラスな雰囲気を演出し、Yellow属性を軸としながらColorlessのファントムも交えることで属性対策の幅を持たせた設計にしています。3波構成（0.25秒後・1.5秒後・3.0秒後）で合計18体（最低15体以上の要件を満たす）が登場します。各波の出現タイミングと敵種の切り替えによって、単調さを排除しつつ適度なプレッシャーを与えるバトル体験を目指します。フロア係数 1.00 基準での設計であり、全行 aura_type=Default、フェーズ切り替えなしのシンプル構成です。</t>
+          <t>「姫様"拷問"の時間です」の世界観を反映したノーマルブロックです。たこ焼き（Yellow属性・攻撃ロール）、バタートースト（Yellow属性・防御ロール）、ラーメン（Yellow属性・攻撃ロール）、ファントム（Colorless属性・攻撃ロール）の4種が時間差で出現します。同作の料理系の敵キャラを中心に構成することで作品らしいユーモラスな雰囲気を演出し、Yellow属性を軸としながらColorlessのファントムも交えることで属性対策の幅を持たせた設計にしています。3波構成（0.25秒後・1.5秒後・3.0秒後）で合計18体（最低15体以上の要件を満たす）が登場します。各波の出現タイミングと敵種の切り替えによって、単調さを排除しつつ適度なプレッシャーを与えるバトル体験を目指します。フロア係数 1.00 基準での設計であり、全行 aura_type=Default、フェーズ切り替えなしのシンプル構成です。</t>
         </is>
       </c>
       <c r="C4" s="27" t="n"/>
@@ -980,7 +980,11 @@
           <t>3コマ</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr"/>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>gom_00003</t>
+        </is>
+      </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
           <t>None</t>
@@ -1011,7 +1015,11 @@
           <t>2コマ</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr"/>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>gom_00003</t>
+        </is>
+      </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
           <t>None</t>
@@ -1042,7 +1050,11 @@
           <t>4コマ</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr"/>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>gom_00003</t>
+        </is>
+      </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
           <t>None</t>
@@ -1277,7 +1289,7 @@
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>雑魚</t>
+          <t>雑魚（e_キャラ）</t>
         </is>
       </c>
       <c r="J26" s="2" t="n"/>
@@ -1318,7 +1330,7 @@
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
-          <t>雑魚</t>
+          <t>雑魚（e_キャラ）</t>
         </is>
       </c>
       <c r="J27" s="2" t="n"/>
@@ -1359,7 +1371,7 @@
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
-          <t>雑魚</t>
+          <t>雑魚（e_キャラ）</t>
         </is>
       </c>
       <c r="J28" s="2" t="n"/>
@@ -1616,7 +1628,11 @@
       <c r="G40" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="26" t="inlineStr"/>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>開幕250ms・3体</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
@@ -1651,7 +1667,7 @@
       </c>
       <c r="H41" s="26" t="inlineStr">
         <is>
-          <t>同タイミング</t>
+          <t>同時250ms・3体</t>
         </is>
       </c>
       <c r="I41" s="2" t="n"/>
@@ -1686,7 +1702,11 @@
       <c r="G42" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="26" t="inlineStr"/>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>1500ms・4体</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
@@ -1719,7 +1739,11 @@
       <c r="G43" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H43" s="26" t="inlineStr"/>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>3000ms・4体</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
@@ -1754,7 +1778,7 @@
       </c>
       <c r="H44" s="26" t="inlineStr">
         <is>
-          <t>同タイミング</t>
+          <t>同時3000ms・4体・合計18体</t>
         </is>
       </c>
       <c r="I44" s="2" t="n"/>
@@ -1977,7 +2001,7 @@
           <t>バトルヒント</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr"/>
+      <c r="C58" s="18" t="inlineStr"/>
       <c r="D58" s="27" t="n"/>
       <c r="E58" s="27" t="n"/>
       <c r="F58" s="27" t="n"/>
@@ -1996,7 +2020,7 @@
           <t>ステージ説明文</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr"/>
+      <c r="C59" s="18" t="inlineStr"/>
       <c r="D59" s="27" t="n"/>
       <c r="E59" s="27" t="n"/>
       <c r="F59" s="27" t="n"/>
@@ -2389,7 +2413,11 @@
         </is>
       </c>
       <c r="AD2" s="31" t="inlineStr"/>
-      <c r="AE2" s="31" t="inlineStr"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF2" s="31" t="inlineStr"/>
       <c r="AG2" s="31" t="inlineStr">
         <is>
@@ -2506,7 +2534,11 @@
         </is>
       </c>
       <c r="AD3" s="31" t="inlineStr"/>
-      <c r="AE3" s="31" t="inlineStr"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF3" s="31" t="inlineStr"/>
       <c r="AG3" s="31" t="inlineStr">
         <is>
@@ -2623,7 +2655,11 @@
         </is>
       </c>
       <c r="AD4" s="31" t="inlineStr"/>
-      <c r="AE4" s="31" t="inlineStr"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF4" s="31" t="inlineStr"/>
       <c r="AG4" s="31" t="inlineStr">
         <is>
@@ -2740,7 +2776,11 @@
         </is>
       </c>
       <c r="AD5" s="31" t="inlineStr"/>
-      <c r="AE5" s="31" t="inlineStr"/>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF5" s="31" t="inlineStr"/>
       <c r="AG5" s="31" t="inlineStr">
         <is>
@@ -2857,7 +2897,11 @@
         </is>
       </c>
       <c r="AD6" s="31" t="inlineStr"/>
-      <c r="AE6" s="31" t="inlineStr"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AF6" s="31" t="inlineStr"/>
       <c r="AG6" s="31" t="inlineStr">
         <is>
@@ -3842,13 +3886,21 @@
           <t>7</t>
         </is>
       </c>
-      <c r="G2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr">
+        <is>
+          <t>gom_00003</t>
+        </is>
+      </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="I2" s="31" t="inlineStr"/>
+      <c r="I2" s="31" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
       <c r="J2" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -4023,13 +4075,21 @@
           <t>6</t>
         </is>
       </c>
-      <c r="G3" s="31" t="inlineStr"/>
+      <c r="G3" s="31" t="inlineStr">
+        <is>
+          <t>gom_00003</t>
+        </is>
+      </c>
       <c r="H3" s="31" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I3" s="31" t="inlineStr"/>
+      <c r="I3" s="31" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
           <t>None</t>
@@ -4200,13 +4260,21 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>gom_00003</t>
+        </is>
+      </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr"/>
+      <c r="I4" s="31" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
       <c r="J4" s="31" t="inlineStr">
         <is>
           <t>None</t>
